--- a/Book3.xlsx
+++ b/Book3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A380C00F-E83A-4314-9799-5B9F87BBF3C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4AF6A61-5A64-45DE-AEE1-B328FB168444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{D697ACCF-D99D-4139-BB70-F0F47AE96BD3}"/>
+    <workbookView xWindow="9518" yWindow="0" windowWidth="9765" windowHeight="11363" xr2:uid="{D697ACCF-D99D-4139-BB70-F0F47AE96BD3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -126,10 +126,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <charset val="1"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -159,7 +161,117 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="15">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -532,30 +644,34 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A24AA759-CFCB-49D2-AAFC-DF8FBD699E22}">
   <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="12.796875" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -820,20 +936,12 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A11">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
-      <formula>"Jigglypuff"</formula>
+  <conditionalFormatting sqref="H15">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+      <formula>"Eevee"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
-      <formula>"Jigglepuff"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:H11">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
-      <formula>50</formula>
+      <formula>"Eevee"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
